--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3617-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3617-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08CBD428-2718-4B7C-86B9-302BCE6FC5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{588DAF28-FAA1-4AA6-ABD0-216FEE27CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{80E8113E-55A0-4E68-86DD-6CC2E15AB46A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6D171234-465B-40E4-ADD0-F1856FCADBF4}"/>
   </bookViews>
   <sheets>
     <sheet name="3617-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,30 +1508,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6191924-74B7-4BB7-93CF-9205EC94C9F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7B0B00-5BC4-403F-BB7C-8510093134B9}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1721,7 +1721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2020</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2019</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2018</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2016</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2015</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2014</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2013</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2012</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2011</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2010</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2009</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2008</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2007</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37" t="s">
         <v>57</v>
       </c>
